--- a/data/kocaeli/service_status.xlsx
+++ b/data/kocaeli/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,8 +762,6 @@
           <t>Servis</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Toplu servise alındı</t>
@@ -775,6 +773,328 @@
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:43:06</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4120</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:43:07</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:43:07</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4122</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:43:07</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:43:07</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:43:07</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:43:07</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4126</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:43:07</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:43:07</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:43:07</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>admin</t>
         </is>

--- a/data/kocaeli/service_status.xlsx
+++ b/data/kocaeli/service_status.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,8 +1082,6 @@
           <t>Servis</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Toplu servise alındı</t>
@@ -1097,6 +1095,963 @@
       <c r="H21" t="inlineStr">
         <is>
           <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:37</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4120</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:18</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:18</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4122</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:18</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:18</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:18</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:18</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4126</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:18</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:18</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:18</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:18</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:19</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:19</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4132</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:19</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4133</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:18:19</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:24</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>4120</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:24</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:24</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4122</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:24</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:24</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:25</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:25</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4126</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:25</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:25</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:25</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:25</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:25</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:25</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>4132</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:26</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4133</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:19:26</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>mciftci</t>
         </is>
       </c>
     </row>

--- a/data/kocaeli/service_status.xlsx
+++ b/data/kocaeli/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2037,8 +2037,6 @@
           <t>Servis</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>Toplu servise alındı</t>
@@ -2052,6 +2050,328 @@
       <c r="H51" t="inlineStr">
         <is>
           <t>mciftci</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:51:21</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4120</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:51:21</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:51:21</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>4122</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:51:21</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:51:21</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:51:21</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:51:21</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>4126</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:51:21</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:51:21</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:51:21</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>admin</t>
         </is>
       </c>
     </row>
